--- a/files/港岛-黄泥涌-Eight Kwai Fong Happy Valley.xlsx
+++ b/files/港岛-黄泥涌-Eight Kwai Fong Happy Valley.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eight Kwai Fong Happy Valley 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,36 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -170,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -186,51 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3316,7 +3183,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-11-12</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4750,7 +4617,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-05</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -4796,7 +4663,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-05</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -5080,7 +4947,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-11-12</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -5364,7 +5231,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -5410,7 +5277,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -5694,7 +5561,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-11-18</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -5932,7 +5799,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-11-25</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -5978,7 +5845,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-20</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -6170,7 +6037,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -6262,7 +6129,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-03-29</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -6454,7 +6321,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-11-15</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -6546,7 +6413,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-01-12</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -7022,7 +6889,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-11-18</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -7068,7 +6935,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-11-18</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -7114,7 +6981,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-11-23</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -7306,7 +7173,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -7352,7 +7219,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -7398,7 +7265,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -7444,7 +7311,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -7582,7 +7449,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -7628,7 +7495,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -7720,7 +7587,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-01-12</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -7858,7 +7725,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-11-17</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -7904,7 +7771,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-03-10</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -8218,1569 +8085,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Eight Kwai Fong Happy Valley - Eight Kwai Fong Happy Valley 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>156 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>9 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>6 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>26 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>24 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>91 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 411呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 395呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 264呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 265呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>E | 392呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>F | 428呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 410呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 401呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 258呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 258呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>E | 398呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>F | 428呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 411呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 401呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 258呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 258呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 398呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 410呎 (1房)
-$1,716万
-$41,844/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 402呎 (1房)
-$1,705万
-$42,418/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 258呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 258呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>E | 397呎 (1房)
-$1,612万
-$40,610/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>F | 426呎 (1房)
-$1,652万
-$38,779/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 411呎 (1房)
-$1,687万
-$41,044/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 401呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 258呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 259呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 397呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 428呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 410呎 (1房)
-$1,662万
-$40,537/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 402呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 258呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 258呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>E | 397呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 410呎 (1房)
-$1,637万
-$39,937/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 402呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 258呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 258呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>E | 398呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>F | 428呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A | 411呎 (1房)
-$1,613万
-$39,251/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 401呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 258呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>D | 258呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>E | 397呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>A | 411呎 (1房)
-$1,494万
-$36,350/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 402呎 (1房)
-$1,580万
-$39,296/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 258呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 258呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>E | 398呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>F | 428呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 410呎 (1房)
-$1,566万
-$38,193/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 401呎 (1房)
-$1,556万
-$38,813/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 258呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>D | 259呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>E | 398呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>F | 428呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 410呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 402呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 258呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 259呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>E | 398呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 411呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 402呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 258呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>D | 259呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>E | 398呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>F | 428呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 411呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 402呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 258呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>D | 259呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>E | 398呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>F | 428呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>A | 410呎 (1房)
-$1,387万
-$33,824/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>B | 401呎 (1房)
-$1,378万
-$34,374/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 258呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>D | 258呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>E | 397呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>F | 428呎 (1房)
-$1,449万
-$33,855/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>A | 410呎 (1房)
-$1,454万
-$35,451/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>B | 402呎 (1房)
-$1,445万
-$35,938/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 258呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>D | 259呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>E | 398呎 (1房)
-$1,382万
-$34,729/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>F | 426呎 (1房)
-$1,430万
-$33,577/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>A | 410呎 (1房)
-$1,432万
-$34,929/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>B | 401呎 (1房)
-$1,423万
-$35,496/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 258呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 258呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F21" s="20" t="inlineStr">
-        <is>
-          <t>E | 398呎 (1房)
-$1,364万
-$34,281/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>F | 426呎 (1房)
-$1,412万
-$33,146/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 410呎 (1房)
-$1,452万
-$35,410/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 402呎 (1房)
-$1,443万
-$35,896/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 258呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>D | 259呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F22" s="20" t="inlineStr">
-        <is>
-          <t>E | 398呎 (1房)
-$1,347万
-$33,842/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G22" s="19" t="inlineStr">
-        <is>
-          <t>F | 426呎 (1房)
-$1,394万
-$32,721/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>A | 410呎 (1房)
-$1,390万
-$33,905/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>B | 401呎 (1房)
-$1,396万
-$34,800/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 258呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>D | 259呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F23" s="20" t="inlineStr">
-        <is>
-          <t>E | 398呎 (1房)
-$1,330万
-$33,407/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G23" s="19" t="inlineStr">
-        <is>
-          <t>F | 426呎 (1房)
-$1,376万
-$32,303/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>A | 411呎 (1房)
-$1,370万
-$33,321/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>B | 401呎 (1房)
-$1,375万
-$34,284/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>C | 258呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>D | 259呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F24" s="20" t="inlineStr">
-        <is>
-          <t>E | 398呎 (1房)
-$1,313万
-$32,980/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G24" s="19" t="inlineStr">
-        <is>
-          <t>F | 426呎 (1房)
-$1,358万
-$31,887/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
-        <is>
-          <t>A | 410呎 (1房)
-$1,268万
-$30,934/呎
-(20年-10月)</t>
-        </is>
-      </c>
-      <c r="C25" s="19" t="inlineStr">
-        <is>
-          <t>B | 401呎 (1房)
-$1,273万
-$31,751/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 258呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>D | 258呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F25" s="20" t="inlineStr">
-        <is>
-          <t>E | 398呎 (1房)
-$1,296万
-$32,555/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G25" s="19" t="inlineStr">
-        <is>
-          <t>F | 426呎 (1房)
-$1,341万
-$31,479/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="inlineStr">
-        <is>
-          <t>A | 410呎 (1房)
-$1,329万
-$32,422/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C26" s="20" t="inlineStr">
-        <is>
-          <t>B | 401呎 (1房)
-$1,334万
-$33,279/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>C | 258呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>D | 259呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>E | 397呎 (1房)
-$1,279万
-$32,219/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G26" s="19" t="inlineStr">
-        <is>
-          <t>F | 428呎 (1房)
-$1,324万
-$30,930/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="inlineStr">
-        <is>
-          <t>A | 410呎 (1房)
-$1,312万
-$32,010/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C27" s="19" t="inlineStr">
-        <is>
-          <t>B | 402呎 (1房)
-$1,239万
-$30,813/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>C | 258呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>D | 259呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F27" s="20" t="inlineStr">
-        <is>
-          <t>E | 398呎 (1房)
-$1,234万
-$30,992/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G27" s="17" t="inlineStr">
-        <is>
-          <t>F | 428呎 (1房)
-$1,279万
-$29,879/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B28" s="19" t="inlineStr">
-        <is>
-          <t>A | 410呎 (1房)
-$1,293万
-$31,537/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C28" s="19" t="inlineStr">
-        <is>
-          <t>B | 401呎 (1房)
-$1,299万
-$32,392/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>C | 258呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E28" s="16" t="inlineStr">
-        <is>
-          <t>D | 258呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="inlineStr">
-        <is>
-          <t>E | 398呎 (1房)
-$1,218万
-$30,598/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G28" s="19" t="inlineStr">
-        <is>
-          <t>F | 426呎 (1房)
-$1,242万
-$29,164/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B29" s="19" t="inlineStr">
-        <is>
-          <t>A | 410呎 (1房)
-$1,274万
-$31,071/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C29" s="19" t="inlineStr">
-        <is>
-          <t>B | 401呎 (1房)
-$1,280万
-$31,925/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>C | 258呎 (开放式)
-$946万
-$36,655/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>D | 258呎 (开放式)
-$938万
-$36,368/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F29" s="19" t="inlineStr">
-        <is>
-          <t>E | 397呎 (1房)
-$1,202万
-$30,282/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G29" s="19" t="inlineStr">
-        <is>
-          <t>F | 426呎 (1房)
-$1,206万
-$28,310/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B30" s="19" t="inlineStr">
-        <is>
-          <t>A | 410呎 (1房)
-$1,281万
-$31,249/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C30" s="19" t="inlineStr">
-        <is>
-          <t>B | 402呎 (1房)
-$1,176万
-$29,246/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>C | 258呎 (开放式)
-$941万
-$36,473/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>D | 258呎 (开放式)
-$934万
-$36,190/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F30" s="19" t="inlineStr">
-        <is>
-          <t>E | 397呎 (1房)
-$1,154万
-$29,076/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G30" s="17" t="inlineStr">
-        <is>
-          <t>F | 428呎 (1房)
-$1,183万
-$27,645/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>A | 410呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>B | 401呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D31" s="18" t="inlineStr">
-        <is>
-          <t>C | 258呎 (开放式)
-$905万
-$35,070/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E31" s="18" t="inlineStr">
-        <is>
-          <t>D | 258呎 (开放式)
-$898万
-$34,795/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F31" s="16" t="inlineStr">
-        <is>
-          <t>E | 397呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G31" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-黄泥涌-Eight Kwai Fong Happy Valley.xlsx
+++ b/files/港岛-黄泥涌-Eight Kwai Fong Happy Valley.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eight Kwai Fong Happy Valley" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,107 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +153,36 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +228,63 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +661,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -8085,4 +8272,1569 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Eight Kwai Fong Happy Valley 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 411呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 395呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 264呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 265呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 392呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 428呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 410呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 401呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 258呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 258呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 398呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 428呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 411呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 401呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 258呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 258呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 398呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 410呎 (1房)
+$1716万
+$41,844/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 402呎 (1房)
+$1705万
+$42,418/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 258呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 258呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 397呎 (1房)
+$1612万
+$40,610/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>F | 426呎 (1房)
+$1652万
+$38,779/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 411呎 (1房)
+$1687万
+$41,044/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 401呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 258呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 259呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 397呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 428呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 410呎 (1房)
+$1662万
+$40,537/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 402呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 258呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 258呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 397呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 410呎 (1房)
+$1637万
+$39,937/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 402呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 258呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 258呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 398呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>F | 428呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 411呎 (1房)
+$1613万
+$39,251/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 401呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 258呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 258呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 397呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>A | 411呎 (1房)
+$1494万
+$36,350/呎
+(20年-11月)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 402呎 (1房)
+$1580万
+$39,296/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 258呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 258呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 398呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 428呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 410呎 (1房)
+$1566万
+$38,193/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 401呎 (1房)
+$1556万
+$38,813/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 258呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 259呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 398呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 428呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 410呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 402呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 258呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 259呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 398呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 411呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 402呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 258呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 259呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 398呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 428呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 411呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 402呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 258呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 259呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 398呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 428呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>A | 410呎 (1房)
+$1387万
+$33,824/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>B | 401呎 (1房)
+$1378万
+$34,374/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 258呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 258呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 397呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 428呎 (1房)
+$1449万
+$33,855/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>A | 410呎 (1房)
+$1454万
+$35,451/呎
+(20年-11月)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 402呎 (1房)
+$1445万
+$35,938/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 258呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 259呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>E | 398呎 (1房)
+$1382万
+$34,729/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>F | 426呎 (1房)
+$1430万
+$33,577/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>A | 410呎 (1房)
+$1432万
+$34,929/呎
+(20年-11月)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 401呎 (1房)
+$1423万
+$35,496/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 258呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 258呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>E | 398呎 (1房)
+$1364万
+$34,281/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>F | 426呎 (1房)
+$1412万
+$33,146/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 410呎 (1房)
+$1452万
+$35,410/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 402呎 (1房)
+$1443万
+$35,896/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 258呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 259呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>E | 398呎 (1房)
+$1347万
+$33,842/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>F | 426呎 (1房)
+$1394万
+$32,721/呎
+(21年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>A | 410呎 (1房)
+$1390万
+$33,905/呎
+(20年-11月)</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>B | 401呎 (1房)
+$1396万
+$34,800/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 258呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 259呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>E | 398呎 (1房)
+$1330万
+$33,407/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G22" s="23" t="inlineStr">
+        <is>
+          <t>F | 426呎 (1房)
+$1376万
+$32,303/呎
+(20年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 411呎 (1房)
+$1370万
+$33,321/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>B | 401呎 (1房)
+$1375万
+$34,284/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 258呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 259呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>E | 398呎 (1房)
+$1313万
+$32,980/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G23" s="23" t="inlineStr">
+        <is>
+          <t>F | 426呎 (1房)
+$1358万
+$31,887/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>A | 410呎 (1房)
+$1268万
+$30,934/呎
+(20年-10月)</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>B | 401呎 (1房)
+$1273万
+$31,751/呎
+(20年-11月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 258呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 258呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>E | 398呎 (1房)
+$1296万
+$32,555/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G24" s="23" t="inlineStr">
+        <is>
+          <t>F | 426呎 (1房)
+$1341万
+$31,479/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>A | 410呎 (1房)
+$1329万
+$32,422/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>B | 401呎 (1房)
+$1334万
+$33,279/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 258呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 259呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>E | 397呎 (1房)
+$1279万
+$32,219/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G25" s="23" t="inlineStr">
+        <is>
+          <t>F | 428呎 (1房)
+$1324万
+$30,930/呎
+(21年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>A | 410呎 (1房)
+$1312万
+$32,010/呎
+(20年-11月)</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>B | 402呎 (1房)
+$1239万
+$30,813/呎
+(20年-11月)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 258呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 259呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>E | 398呎 (1房)
+$1234万
+$30,992/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>F | 428呎 (1房)
+$1279万
+$29,879/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>A | 410呎 (1房)
+$1293万
+$31,537/呎
+(20年-11月)</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>B | 401呎 (1房)
+$1299万
+$32,392/呎
+(20年-11月)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 258呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 258呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>E | 398呎 (1房)
+$1218万
+$30,598/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G27" s="23" t="inlineStr">
+        <is>
+          <t>F | 426呎 (1房)
+$1242万
+$29,164/呎
+(20年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>A | 410呎 (1房)
+$1274万
+$31,071/呎
+(20年-11月)</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>B | 401呎 (1房)
+$1280万
+$31,925/呎
+(20年-11月)</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>C | 258呎 (开放式)
+$946万
+$36,655/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>D | 258呎 (开放式)
+$938万
+$36,368/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="inlineStr">
+        <is>
+          <t>E | 397呎 (1房)
+$1202万
+$30,282/呎
+(22年-04月)</t>
+        </is>
+      </c>
+      <c r="G28" s="23" t="inlineStr">
+        <is>
+          <t>F | 426呎 (1房)
+$1206万
+$28,310/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>A | 410呎 (1房)
+$1281万
+$31,249/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>B | 402呎 (1房)
+$1176万
+$29,246/呎
+(20年-11月)</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>C | 258呎 (开放式)
+$941万
+$36,473/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>D | 258呎 (开放式)
+$934万
+$36,190/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>E | 397呎 (1房)
+$1154万
+$29,076/呎
+(21年-01月)</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
+        <is>
+          <t>F | 428呎 (1房)
+$1183万
+$27,645/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 410呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 401呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>C | 258呎 (开放式)
+$905万
+$35,070/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>D | 258呎 (开放式)
+$898万
+$34,795/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>E | 397呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G30" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-黄泥涌-Eight Kwai Fong Happy Valley.xlsx
+++ b/files/港岛-黄泥涌-Eight Kwai Fong Happy Valley.xlsx
@@ -661,7 +661,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-黄泥涌-Eight Kwai Fong Happy Valley.xlsx
+++ b/files/港岛-黄泥涌-Eight Kwai Fong Happy Valley.xlsx
@@ -651,7 +651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J158"/>
+  <dimension ref="A1:N158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -664,6 +664,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -721,6 +725,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -771,6 +795,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -821,6 +865,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -871,6 +935,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -921,6 +1005,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -971,6 +1075,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1021,6 +1145,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1071,6 +1215,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1121,6 +1285,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1171,6 +1355,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1221,6 +1425,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1271,6 +1495,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1321,6 +1565,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1371,6 +1635,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1421,6 +1705,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1471,6 +1775,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1521,6 +1845,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1571,6 +1915,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1621,6 +1985,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1667,6 +2051,22 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>15941800</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>37422</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1713,6 +2113,22 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>15557730</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>39188</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1763,6 +2179,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1813,6 +2249,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1859,6 +2315,22 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>16455180</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>40933</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1905,6 +2377,22 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>16555540</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>40379</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1955,6 +2443,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2005,6 +2513,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2055,6 +2583,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2105,6 +2653,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2155,6 +2723,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2201,6 +2789,22 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>16278585</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>39607</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2251,6 +2855,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2301,6 +2925,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2351,6 +2995,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2401,6 +3065,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2451,6 +3135,26 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2497,6 +3201,22 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>16038300</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>39118</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2547,6 +3267,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2597,6 +3337,26 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2647,6 +3407,26 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2697,6 +3477,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2747,6 +3547,26 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2793,6 +3613,22 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>15800910</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>38539</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2843,6 +3679,26 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2893,6 +3749,26 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2943,6 +3819,26 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2993,6 +3889,26 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3043,6 +3959,26 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3089,6 +4025,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>15567380</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>37877</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3139,6 +4091,26 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3189,6 +4161,26 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3239,6 +4231,26 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3289,6 +4301,26 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3335,6 +4367,22 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>15244105</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>37921</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3381,6 +4429,22 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>14940000</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>36350</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3431,6 +4495,26 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3481,6 +4565,26 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3531,6 +4635,26 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3581,6 +4705,26 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3627,6 +4771,22 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>15019260</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>37455</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3673,6 +4833,22 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>15110935</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>36856</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3723,6 +4899,26 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3773,6 +4969,26 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3823,6 +5039,26 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3873,6 +5109,26 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3923,6 +5179,26 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3973,6 +5249,26 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4023,6 +5319,26 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4073,6 +5389,26 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4123,6 +5459,26 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4173,6 +5529,26 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4223,6 +5599,26 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4273,6 +5669,26 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4323,6 +5739,26 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4373,6 +5809,26 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4423,6 +5879,26 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4473,6 +5949,26 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4523,6 +6019,26 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4573,6 +6089,26 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4619,6 +6155,22 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>13982850</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>32670</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4669,6 +6221,26 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4719,6 +6291,26 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4769,6 +6361,26 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4815,6 +6427,22 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>13784000</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>34374</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4861,6 +6489,22 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>13868000</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>33824</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4907,6 +6551,22 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>13803360</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>32402</v>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4953,6 +6613,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>13338230</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>33513</v>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5003,6 +6679,26 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5053,6 +6749,26 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5099,6 +6815,22 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>13941355</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>34680</v>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5145,6 +6877,22 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>14535000</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>35451</v>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5191,6 +6939,22 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>13625800</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>31985</v>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5237,6 +7001,22 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>13166460</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>33082</v>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5287,6 +7067,26 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L95" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5337,6 +7137,26 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5383,6 +7203,22 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>13735810</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>34254</v>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5429,6 +7265,22 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>14321000</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>34929</v>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5475,6 +7327,22 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>13939000</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>32721</v>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5521,6 +7389,22 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>12997585</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>32657</v>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5571,6 +7455,26 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5621,6 +7525,26 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5667,6 +7591,22 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>13924950</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>34639</v>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5713,6 +7653,22 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>14009870</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>34170</v>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5759,6 +7715,22 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>13761000</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>32303</v>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5805,6 +7777,22 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>12830640</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>32238</v>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5855,6 +7843,26 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5905,6 +7913,26 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5951,6 +7979,22 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>13466575</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>33582</v>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5997,6 +8041,22 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="n">
+        <v>13901000</v>
+      </c>
+      <c r="L110" s="5" t="n">
+        <v>33905</v>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6043,6 +8103,22 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="n">
+        <v>13584000</v>
+      </c>
+      <c r="L111" s="5" t="n">
+        <v>31887</v>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6089,6 +8165,22 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>12666590</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>31826</v>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6139,6 +8231,26 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L113" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6189,6 +8301,26 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6235,6 +8367,22 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="n">
+        <v>13748000</v>
+      </c>
+      <c r="L115" s="5" t="n">
+        <v>34284</v>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6281,6 +8429,22 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="n">
+        <v>13215675</v>
+      </c>
+      <c r="L116" s="5" t="n">
+        <v>32155</v>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6327,6 +8491,22 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="n">
+        <v>13410000</v>
+      </c>
+      <c r="L117" s="5" t="n">
+        <v>31479</v>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6373,6 +8553,22 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>12503505</v>
+      </c>
+      <c r="L118" s="5" t="n">
+        <v>31416</v>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6423,6 +8619,26 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L119" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6473,6 +8689,26 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L120" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6519,6 +8755,22 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="n">
+        <v>12732000</v>
+      </c>
+      <c r="L121" s="5" t="n">
+        <v>31751</v>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6565,6 +8817,22 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="n">
+        <v>12683000</v>
+      </c>
+      <c r="L122" s="5" t="n">
+        <v>30934</v>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6611,6 +8879,22 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="n">
+        <v>13238000</v>
+      </c>
+      <c r="L123" s="5" t="n">
+        <v>30930</v>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6657,6 +8941,22 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="n">
+        <v>12343315</v>
+      </c>
+      <c r="L124" s="5" t="n">
+        <v>31091</v>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6707,6 +9007,26 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L125" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6757,6 +9077,26 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L126" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6803,6 +9143,22 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="n">
+        <v>12877925</v>
+      </c>
+      <c r="L127" s="5" t="n">
+        <v>32115</v>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6849,6 +9205,22 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="n">
+        <v>12827745</v>
+      </c>
+      <c r="L128" s="5" t="n">
+        <v>31287</v>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6895,6 +9267,22 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="n">
+        <v>12340420</v>
+      </c>
+      <c r="L129" s="5" t="n">
+        <v>28833</v>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6941,6 +9329,22 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="n">
+        <v>11903275</v>
+      </c>
+      <c r="L130" s="5" t="n">
+        <v>29908</v>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6991,6 +9395,26 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L131" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7041,6 +9465,26 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L132" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7087,6 +9531,22 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="n">
+        <v>12387000</v>
+      </c>
+      <c r="L133" s="5" t="n">
+        <v>30813</v>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7133,6 +9593,22 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="n">
+        <v>13124000</v>
+      </c>
+      <c r="L134" s="5" t="n">
+        <v>32010</v>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7179,6 +9655,22 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="n">
+        <v>12424000</v>
+      </c>
+      <c r="L135" s="5" t="n">
+        <v>29164</v>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7225,6 +9717,22 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="n">
+        <v>11751770</v>
+      </c>
+      <c r="L136" s="5" t="n">
+        <v>29527</v>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7275,6 +9783,26 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L137" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7325,6 +9853,26 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L138" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7371,6 +9919,22 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="5" t="n">
+        <v>12989000</v>
+      </c>
+      <c r="L139" s="5" t="n">
+        <v>32392</v>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7417,6 +9981,22 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="n">
+        <v>12930000</v>
+      </c>
+      <c r="L140" s="5" t="n">
+        <v>31537</v>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7463,6 +10043,22 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="5" t="n">
+        <v>12060000</v>
+      </c>
+      <c r="L141" s="5" t="n">
+        <v>28310</v>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7509,6 +10105,22 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="n">
+        <v>12022000</v>
+      </c>
+      <c r="L142" s="5" t="n">
+        <v>30282</v>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7555,6 +10167,22 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K143" s="5" t="n">
+        <v>9054595</v>
+      </c>
+      <c r="L143" s="5" t="n">
+        <v>35095</v>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7601,6 +10229,22 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K144" s="5" t="n">
+        <v>9126005</v>
+      </c>
+      <c r="L144" s="5" t="n">
+        <v>35372</v>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7647,6 +10291,22 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="5" t="n">
+        <v>12802000</v>
+      </c>
+      <c r="L145" s="5" t="n">
+        <v>31925</v>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7693,6 +10353,22 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" s="5" t="n">
+        <v>12739000</v>
+      </c>
+      <c r="L146" s="5" t="n">
+        <v>31071</v>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7739,6 +10415,22 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K147" s="5" t="n">
+        <v>11417880</v>
+      </c>
+      <c r="L147" s="5" t="n">
+        <v>26677</v>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7785,6 +10477,22 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="n">
+        <v>11543000</v>
+      </c>
+      <c r="L148" s="5" t="n">
+        <v>29076</v>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7831,6 +10539,22 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K149" s="5" t="n">
+        <v>9010205</v>
+      </c>
+      <c r="L149" s="5" t="n">
+        <v>34923</v>
+      </c>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N149" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7877,6 +10601,22 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="n">
+        <v>9080650</v>
+      </c>
+      <c r="L150" s="5" t="n">
+        <v>35196</v>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7923,6 +10663,22 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" s="5" t="n">
+        <v>11757000</v>
+      </c>
+      <c r="L151" s="5" t="n">
+        <v>29246</v>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7969,6 +10725,22 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="n">
+        <v>12812000</v>
+      </c>
+      <c r="L152" s="5" t="n">
+        <v>31249</v>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8019,6 +10791,26 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L153" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8069,6 +10861,26 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L154" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8115,6 +10927,22 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K155" s="5" t="n">
+        <v>8662805</v>
+      </c>
+      <c r="L155" s="5" t="n">
+        <v>33577</v>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8161,6 +10989,22 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K156" s="5" t="n">
+        <v>8731320</v>
+      </c>
+      <c r="L156" s="5" t="n">
+        <v>33842</v>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>120天成交計劃</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8211,6 +11055,26 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L157" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8261,13 +11125,33 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K158" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L158" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -8851,7 +11735,7 @@
           <t>A | 411呎 (1房)
 $1494万
 $36,350/呎
-(20年-11月)</t>
+(20年-11月-12日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -9126,7 +12010,7 @@
           <t>A | 410呎 (1房)
 $1387万
 $33,824/呎
-(21年-12月)</t>
+(21年-12月-05日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -9134,7 +12018,7 @@
           <t>B | 401呎 (1房)
 $1378万
 $34,374/呎
-(21年-12月)</t>
+(21年-12月-05日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -9181,7 +12065,7 @@
           <t>A | 410呎 (1房)
 $1454万
 $35,451/呎
-(20年-11月)</t>
+(20年-11月-12日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -9236,7 +12120,7 @@
           <t>A | 410呎 (1房)
 $1432万
 $34,929/呎
-(20年-11月)</t>
+(20年-11月-11日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -9331,7 +12215,7 @@
           <t>F | 426呎 (1房)
 $1394万
 $32,721/呎
-(21年-06月)</t>
+(21年-06月-17日)</t>
         </is>
       </c>
     </row>
@@ -9346,7 +12230,7 @@
           <t>A | 410呎 (1房)
 $1390万
 $33,905/呎
-(20年-11月)</t>
+(20年-11月-25日)</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -9386,7 +12270,7 @@
           <t>F | 426呎 (1房)
 $1376万
 $32,303/呎
-(20年-11月)</t>
+(20年-11月-18日)</t>
         </is>
       </c>
     </row>
@@ -9409,7 +12293,7 @@
           <t>B | 401呎 (1房)
 $1375万
 $34,284/呎
-(21年-03月)</t>
+(21年-03月-02日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -9441,7 +12325,7 @@
           <t>F | 426呎 (1房)
 $1358万
 $31,887/呎
-(20年-12月)</t>
+(20年-12月-20日)</t>
         </is>
       </c>
     </row>
@@ -9456,7 +12340,7 @@
           <t>A | 410呎 (1房)
 $1268万
 $30,934/呎
-(20年-10月)</t>
+(20年-10月-25日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -9464,7 +12348,7 @@
           <t>B | 401呎 (1房)
 $1273万
 $31,751/呎
-(20年-11月)</t>
+(20年-11月-15日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -9496,7 +12380,7 @@
           <t>F | 426呎 (1房)
 $1341万
 $31,479/呎
-(21年-03月)</t>
+(21年-03月-29日)</t>
         </is>
       </c>
     </row>
@@ -9551,7 +12435,7 @@
           <t>F | 428呎 (1房)
 $1324万
 $30,930/呎
-(21年-01月)</t>
+(21年-01月-12日)</t>
         </is>
       </c>
     </row>
@@ -9566,7 +12450,7 @@
           <t>A | 410呎 (1房)
 $1312万
 $32,010/呎
-(20年-11月)</t>
+(20年-11月-18日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -9574,7 +12458,7 @@
           <t>B | 402呎 (1房)
 $1239万
 $30,813/呎
-(20年-11月)</t>
+(20年-11月-18日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -9621,7 +12505,7 @@
           <t>A | 410呎 (1房)
 $1293万
 $31,537/呎
-(20年-11月)</t>
+(20年-11月-11日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -9629,7 +12513,7 @@
           <t>B | 401呎 (1房)
 $1299万
 $32,392/呎
-(20年-11月)</t>
+(20年-11月-11日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -9661,7 +12545,7 @@
           <t>F | 426呎 (1房)
 $1242万
 $29,164/呎
-(20年-11月)</t>
+(20年-11月-23日)</t>
         </is>
       </c>
     </row>
@@ -9676,7 +12560,7 @@
           <t>A | 410呎 (1房)
 $1274万
 $31,071/呎
-(20年-11月)</t>
+(20年-11月-11日)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -9684,7 +12568,7 @@
           <t>B | 401呎 (1房)
 $1280万
 $31,925/呎
-(20年-11月)</t>
+(20年-11月-11日)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -9708,7 +12592,7 @@
           <t>E | 397呎 (1房)
 $1202万
 $30,282/呎
-(22年-04月)</t>
+(22年-04月-28日)</t>
         </is>
       </c>
       <c r="G28" s="23" t="inlineStr">
@@ -9716,7 +12600,7 @@
           <t>F | 426呎 (1房)
 $1206万
 $28,310/呎
-(20年-12月)</t>
+(20年-12月-01日)</t>
         </is>
       </c>
     </row>
@@ -9731,7 +12615,7 @@
           <t>A | 410呎 (1房)
 $1281万
 $31,249/呎
-(21年-03月)</t>
+(21年-03月-10日)</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
@@ -9739,7 +12623,7 @@
           <t>B | 402呎 (1房)
 $1176万
 $29,246/呎
-(20年-11月)</t>
+(20年-11月-17日)</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -9763,7 +12647,7 @@
           <t>E | 397呎 (1房)
 $1154万
 $29,076/呎
-(21年-01月)</t>
+(21年-01月-12日)</t>
         </is>
       </c>
       <c r="G29" s="21" t="inlineStr">

--- a/files/港岛-黄泥涌-Eight Kwai Fong Happy Valley.xlsx
+++ b/files/港岛-黄泥涌-Eight Kwai Fong Happy Valley.xlsx
@@ -2051,7 +2051,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K21" s="5" t="n">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K22" s="5" t="n">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K25" s="5" t="n">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K26" s="5" t="n">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K32" s="5" t="n">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K38" s="5" t="n">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K44" s="5" t="n">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K50" s="5" t="n">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K55" s="5" t="n">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K61" s="5" t="n">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K62" s="5" t="n">
@@ -6155,7 +6155,7 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K81" s="5" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K87" s="5" t="n">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K88" s="5" t="n">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K91" s="5" t="n">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K93" s="5" t="n">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K94" s="5" t="n">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K97" s="5" t="n">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K100" s="5" t="n">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K103" s="5" t="n">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K104" s="5" t="n">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K106" s="5" t="n">
@@ -7979,7 +7979,7 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K109" s="5" t="n">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K112" s="5" t="n">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K116" s="5" t="n">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K118" s="5" t="n">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K124" s="5" t="n">
@@ -9143,7 +9143,7 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K127" s="5" t="n">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K128" s="5" t="n">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K129" s="5" t="n">
@@ -9329,7 +9329,7 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K130" s="5" t="n">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K136" s="5" t="n">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K143" s="5" t="n">
@@ -10229,7 +10229,7 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K144" s="5" t="n">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K147" s="5" t="n">
@@ -10539,7 +10539,7 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K149" s="5" t="n">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K150" s="5" t="n">
@@ -10927,7 +10927,7 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K155" s="5" t="n">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K156" s="5" t="n">

--- a/files/港岛-黄泥涌-Eight Kwai Fong Happy Valley.xlsx
+++ b/files/港岛-黄泥涌-Eight Kwai Fong Happy Valley.xlsx
@@ -11735,7 +11735,7 @@
           <t>A | 411呎 (1房)
 $1494万
 $36,350/呎
-(20年-11月-12日)</t>
+(20年-11月)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -12010,7 +12010,7 @@
           <t>A | 410呎 (1房)
 $1387万
 $33,824/呎
-(21年-12月-05日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -12018,7 +12018,7 @@
           <t>B | 401呎 (1房)
 $1378万
 $34,374/呎
-(21年-12月-05日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -12065,7 +12065,7 @@
           <t>A | 410呎 (1房)
 $1454万
 $35,451/呎
-(20年-11月-12日)</t>
+(20年-11月)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -12120,7 +12120,7 @@
           <t>A | 410呎 (1房)
 $1432万
 $34,929/呎
-(20年-11月-11日)</t>
+(20年-11月)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -12215,7 +12215,7 @@
           <t>F | 426呎 (1房)
 $1394万
 $32,721/呎
-(21年-06月-17日)</t>
+(21年-06月)</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12230,7 @@
           <t>A | 410呎 (1房)
 $1390万
 $33,905/呎
-(20年-11月-25日)</t>
+(20年-11月)</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -12270,7 +12270,7 @@
           <t>F | 426呎 (1房)
 $1376万
 $32,303/呎
-(20年-11月-18日)</t>
+(20年-11月)</t>
         </is>
       </c>
     </row>
@@ -12293,7 +12293,7 @@
           <t>B | 401呎 (1房)
 $1375万
 $34,284/呎
-(21年-03月-02日)</t>
+(21年-03月)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -12325,7 +12325,7 @@
           <t>F | 426呎 (1房)
 $1358万
 $31,887/呎
-(20年-12月-20日)</t>
+(20年-12月)</t>
         </is>
       </c>
     </row>
@@ -12340,7 +12340,7 @@
           <t>A | 410呎 (1房)
 $1268万
 $30,934/呎
-(20年-10月-25日)</t>
+(20年-10月)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -12348,7 +12348,7 @@
           <t>B | 401呎 (1房)
 $1273万
 $31,751/呎
-(20年-11月-15日)</t>
+(20年-11月)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -12380,7 +12380,7 @@
           <t>F | 426呎 (1房)
 $1341万
 $31,479/呎
-(21年-03月-29日)</t>
+(21年-03月)</t>
         </is>
       </c>
     </row>
@@ -12435,7 +12435,7 @@
           <t>F | 428呎 (1房)
 $1324万
 $30,930/呎
-(21年-01月-12日)</t>
+(21年-01月)</t>
         </is>
       </c>
     </row>
@@ -12450,7 +12450,7 @@
           <t>A | 410呎 (1房)
 $1312万
 $32,010/呎
-(20年-11月-18日)</t>
+(20年-11月)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -12458,7 +12458,7 @@
           <t>B | 402呎 (1房)
 $1239万
 $30,813/呎
-(20年-11月-18日)</t>
+(20年-11月)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -12505,7 +12505,7 @@
           <t>A | 410呎 (1房)
 $1293万
 $31,537/呎
-(20年-11月-11日)</t>
+(20年-11月)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -12513,7 +12513,7 @@
           <t>B | 401呎 (1房)
 $1299万
 $32,392/呎
-(20年-11月-11日)</t>
+(20年-11月)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -12545,7 +12545,7 @@
           <t>F | 426呎 (1房)
 $1242万
 $29,164/呎
-(20年-11月-23日)</t>
+(20年-11月)</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
           <t>A | 410呎 (1房)
 $1274万
 $31,071/呎
-(20年-11月-11日)</t>
+(20年-11月)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -12568,7 +12568,7 @@
           <t>B | 401呎 (1房)
 $1280万
 $31,925/呎
-(20年-11月-11日)</t>
+(20年-11月)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -12592,7 +12592,7 @@
           <t>E | 397呎 (1房)
 $1202万
 $30,282/呎
-(22年-04月-28日)</t>
+(22年-04月)</t>
         </is>
       </c>
       <c r="G28" s="23" t="inlineStr">
@@ -12600,7 +12600,7 @@
           <t>F | 426呎 (1房)
 $1206万
 $28,310/呎
-(20年-12月-01日)</t>
+(20年-12月)</t>
         </is>
       </c>
     </row>
@@ -12615,7 +12615,7 @@
           <t>A | 410呎 (1房)
 $1281万
 $31,249/呎
-(21年-03月-10日)</t>
+(21年-03月)</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
@@ -12623,7 +12623,7 @@
           <t>B | 402呎 (1房)
 $1176万
 $29,246/呎
-(20年-11月-17日)</t>
+(20年-11月)</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -12647,7 +12647,7 @@
           <t>E | 397呎 (1房)
 $1154万
 $29,076/呎
-(21年-01月-12日)</t>
+(21年-01月)</t>
         </is>
       </c>
       <c r="G29" s="21" t="inlineStr">

--- a/files/港岛-黄泥涌-Eight Kwai Fong Happy Valley.xlsx
+++ b/files/港岛-黄泥涌-Eight Kwai Fong Happy Valley.xlsx
@@ -11735,7 +11735,7 @@
           <t>A | 411呎 (1房)
 $1494万
 $36,350/呎
-(20年-11月)</t>
+(20年-11月-12日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -12010,7 +12010,7 @@
           <t>A | 410呎 (1房)
 $1387万
 $33,824/呎
-(21年-12月)</t>
+(21年-12月-05日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -12018,7 +12018,7 @@
           <t>B | 401呎 (1房)
 $1378万
 $34,374/呎
-(21年-12月)</t>
+(21年-12月-05日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -12065,7 +12065,7 @@
           <t>A | 410呎 (1房)
 $1454万
 $35,451/呎
-(20年-11月)</t>
+(20年-11月-12日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -12120,7 +12120,7 @@
           <t>A | 410呎 (1房)
 $1432万
 $34,929/呎
-(20年-11月)</t>
+(20年-11月-11日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -12215,7 +12215,7 @@
           <t>F | 426呎 (1房)
 $1394万
 $32,721/呎
-(21年-06月)</t>
+(21年-06月-17日)</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12230,7 @@
           <t>A | 410呎 (1房)
 $1390万
 $33,905/呎
-(20年-11月)</t>
+(20年-11月-25日)</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -12270,7 +12270,7 @@
           <t>F | 426呎 (1房)
 $1376万
 $32,303/呎
-(20年-11月)</t>
+(20年-11月-18日)</t>
         </is>
       </c>
     </row>
@@ -12293,7 +12293,7 @@
           <t>B | 401呎 (1房)
 $1375万
 $34,284/呎
-(21年-03月)</t>
+(21年-03月-02日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -12325,7 +12325,7 @@
           <t>F | 426呎 (1房)
 $1358万
 $31,887/呎
-(20年-12月)</t>
+(20年-12月-20日)</t>
         </is>
       </c>
     </row>
@@ -12340,7 +12340,7 @@
           <t>A | 410呎 (1房)
 $1268万
 $30,934/呎
-(20年-10月)</t>
+(20年-10月-25日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -12348,7 +12348,7 @@
           <t>B | 401呎 (1房)
 $1273万
 $31,751/呎
-(20年-11月)</t>
+(20年-11月-15日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -12380,7 +12380,7 @@
           <t>F | 426呎 (1房)
 $1341万
 $31,479/呎
-(21年-03月)</t>
+(21年-03月-29日)</t>
         </is>
       </c>
     </row>
@@ -12435,7 +12435,7 @@
           <t>F | 428呎 (1房)
 $1324万
 $30,930/呎
-(21年-01月)</t>
+(21年-01月-12日)</t>
         </is>
       </c>
     </row>
@@ -12450,7 +12450,7 @@
           <t>A | 410呎 (1房)
 $1312万
 $32,010/呎
-(20年-11月)</t>
+(20年-11月-18日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -12458,7 +12458,7 @@
           <t>B | 402呎 (1房)
 $1239万
 $30,813/呎
-(20年-11月)</t>
+(20年-11月-18日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -12505,7 +12505,7 @@
           <t>A | 410呎 (1房)
 $1293万
 $31,537/呎
-(20年-11月)</t>
+(20年-11月-11日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -12513,7 +12513,7 @@
           <t>B | 401呎 (1房)
 $1299万
 $32,392/呎
-(20年-11月)</t>
+(20年-11月-11日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -12545,7 +12545,7 @@
           <t>F | 426呎 (1房)
 $1242万
 $29,164/呎
-(20年-11月)</t>
+(20年-11月-23日)</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
           <t>A | 410呎 (1房)
 $1274万
 $31,071/呎
-(20年-11月)</t>
+(20年-11月-11日)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -12568,7 +12568,7 @@
           <t>B | 401呎 (1房)
 $1280万
 $31,925/呎
-(20年-11月)</t>
+(20年-11月-11日)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -12592,7 +12592,7 @@
           <t>E | 397呎 (1房)
 $1202万
 $30,282/呎
-(22年-04月)</t>
+(22年-04月-28日)</t>
         </is>
       </c>
       <c r="G28" s="23" t="inlineStr">
@@ -12600,7 +12600,7 @@
           <t>F | 426呎 (1房)
 $1206万
 $28,310/呎
-(20年-12月)</t>
+(20年-12月-01日)</t>
         </is>
       </c>
     </row>
@@ -12615,7 +12615,7 @@
           <t>A | 410呎 (1房)
 $1281万
 $31,249/呎
-(21年-03月)</t>
+(21年-03月-10日)</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
@@ -12623,7 +12623,7 @@
           <t>B | 402呎 (1房)
 $1176万
 $29,246/呎
-(20年-11月)</t>
+(20年-11月-17日)</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -12647,7 +12647,7 @@
           <t>E | 397呎 (1房)
 $1154万
 $29,076/呎
-(21年-01月)</t>
+(21年-01月-12日)</t>
         </is>
       </c>
       <c r="G29" s="21" t="inlineStr">
